--- a/data/trans_dic/P3A$personadelacasa-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P3A$personadelacasa-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que al menos otra persona se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente otra persona del hogar se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>73,16; 86,38</t>
+          <t>72,45; 86,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>73,91; 84,93</t>
+          <t>73,16; 84,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>75,68; 84,48</t>
+          <t>75,66; 84,6</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>34,87; 46,96</t>
+          <t>34,51; 46,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,3; 35,1</t>
+          <t>17,47; 34,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26,05; 38,82</t>
+          <t>26,36; 38,69</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,82; 23,96</t>
+          <t>16,42; 23,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,68; 42,18</t>
+          <t>15,72; 43,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,58; 34,15</t>
+          <t>17,39; 32,85</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,52; 19,17</t>
+          <t>5,4; 19,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,87; 26,07</t>
+          <t>19,5; 26,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,18; 21,63</t>
+          <t>11,32; 21,81</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,03; 23,64</t>
+          <t>17,23; 23,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,4; 19,11</t>
+          <t>14,23; 18,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,58; 20,44</t>
+          <t>16,4; 20,29</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10,15; 15,75</t>
+          <t>10,07; 15,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,1; 12,2</t>
+          <t>3,22; 12,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,67; 12,69</t>
+          <t>4,3; 12,55</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,13; 14,08</t>
+          <t>7,94; 13,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,8; 17,43</t>
+          <t>12,73; 17,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,53; 15,31</t>
+          <t>11,58; 15,44</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>20,98; 29,13</t>
+          <t>20,6; 28,95</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>20,53; 27,76</t>
+          <t>19,87; 27,64</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22,23; 27,51</t>
+          <t>22,48; 27,55</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que al menos otra persona se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente otra persona del hogar se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>292640; 345496</t>
+          <t>289803; 346683</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>231498; 266007</t>
+          <t>229146; 264792</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>539706; 602513</t>
+          <t>539623; 603343</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>147698; 198880</t>
+          <t>146184; 197591</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>88614; 179729</t>
+          <t>89448; 179144</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>243694; 363204</t>
+          <t>246641; 362017</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>90212; 128484</t>
+          <t>88048; 126021</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>92821; 249724</t>
+          <t>93050; 256779</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>198325; 385290</t>
+          <t>196171; 370671</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>48975; 170219</t>
+          <t>47921; 171445</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>141518; 185682</t>
+          <t>138893; 187909</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>162874; 346045</t>
+          <t>181069; 348949</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>95583; 132658</t>
+          <t>96681; 131233</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>78922; 104697</t>
+          <t>77963; 102371</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>183904; 226755</t>
+          <t>181854; 225080</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>37254; 57812</t>
+          <t>36966; 57740</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>18838; 74173</t>
+          <t>19591; 73746</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>45555; 123740</t>
+          <t>41911; 122370</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>22992; 39805</t>
+          <t>22459; 38544</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>54527; 74219</t>
+          <t>54222; 75394</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>81676; 108450</t>
+          <t>82053; 109375</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>725812; 1007587</t>
+          <t>712530; 1001359</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>761999; 1030299</t>
+          <t>737230; 1025692</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1593901; 1972494</t>
+          <t>1611652; 1974983</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A$personadelacasa-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P3A$personadelacasa-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>78,7%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>72,45; 86,67</t>
+          <t>70,69; 83,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>73,16; 84,54</t>
+          <t>74,26; 84,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>75,66; 84,6</t>
+          <t>73,73; 82,67</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>36,69%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>34,51; 46,65</t>
+          <t>36,01; 48,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,47; 34,98</t>
+          <t>27,22; 36,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26,36; 38,69</t>
+          <t>32,88; 40,34</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>17,67%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,42; 23,5</t>
+          <t>15,88; 22,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,72; 43,37</t>
+          <t>13,9; 18,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,39; 32,85</t>
+          <t>15,91; 19,93</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>21,58%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,4; 19,31</t>
+          <t>15,74; 21,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,5; 26,38</t>
+          <t>22,27; 27,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,32; 21,81</t>
+          <t>19,57; 23,46</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,17%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,23; 23,38</t>
+          <t>16,91; 23,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,23; 18,68</t>
+          <t>14,33; 18,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,4; 20,29</t>
+          <t>16,18; 20,04</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>12,23%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10,07; 15,73</t>
+          <t>10,39; 15,95</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,22; 12,13</t>
+          <t>9,63; 13,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,3; 12,55</t>
+          <t>10,59; 14,11</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,33%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,94; 13,63</t>
+          <t>8,01; 13,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,73; 17,71</t>
+          <t>12,76; 17,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,58; 15,44</t>
+          <t>11,48; 15,33</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>26,46%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>20,6; 28,95</t>
+          <t>25,8; 29,57</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>19,87; 27,64</t>
+          <t>24,02; 26,9</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22,48; 27,55</t>
+          <t>25,24; 27,66</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>323058</t>
+          <t>318476</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>249299</t>
+          <t>287792</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>572356</t>
+          <t>606267</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>289803; 346683</t>
+          <t>288275; 340539</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>229146; 264792</t>
+          <t>269208; 304830</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>539623; 603343</t>
+          <t>567956; 636811</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>172620</t>
+          <t>200368</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>147579</t>
+          <t>158695</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>320199</t>
+          <t>359064</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>146184; 197591</t>
+          <t>171742; 231255</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>89448; 179144</t>
+          <t>136553; 181314</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>246641; 362017</t>
+          <t>321818; 394749</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>107351</t>
+          <t>118120</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>138573</t>
+          <t>101660</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>245923</t>
+          <t>219780</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>88048; 126021</t>
+          <t>98617; 139159</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>93050; 256779</t>
+          <t>86631; 116701</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>196171; 370671</t>
+          <t>197865; 247874</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>117100</t>
+          <t>129634</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>166884</t>
+          <t>180421</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>283984</t>
+          <t>310055</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>47921; 171445</t>
+          <t>110248; 151567</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>138893; 187909</t>
+          <t>163971; 200625</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>181069; 348949</t>
+          <t>281117; 337102</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>112566</t>
+          <t>121542</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>90325</t>
+          <t>99785</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>202891</t>
+          <t>221327</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>96681; 131233</t>
+          <t>103041; 141740</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>77963; 102371</t>
+          <t>87230; 114979</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>181854; 225080</t>
+          <t>197082; 244086</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>47206</t>
+          <t>52489</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>46225</t>
+          <t>50795</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>93431</t>
+          <t>103284</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>36966; 57740</t>
+          <t>42192; 64757</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>19591; 73746</t>
+          <t>42250; 61060</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>41911; 122370</t>
+          <t>89477; 119195</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>30458</t>
+          <t>33504</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>64173</t>
+          <t>69775</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>94631</t>
+          <t>103279</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>22459; 38544</t>
+          <t>24851; 42938</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>54222; 75394</t>
+          <t>59276; 81800</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>82053; 109375</t>
+          <t>88945; 118786</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>910358</t>
+          <t>974134</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>903057</t>
+          <t>948922</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1813415</t>
+          <t>1923057</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>712530; 1001359</t>
+          <t>911085; 1044348</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>737230; 1025692</t>
+          <t>897206; 1004927</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1611652; 1974983</t>
+          <t>1834414; 2009994</t>
         </is>
       </c>
     </row>
